--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102801</v>
+        <v>102807</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102807</v>
+        <v>102809</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102809</v>
+        <v>102810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
